--- a/artfynd/A 30326-2024 artfynd.xlsx
+++ b/artfynd/A 30326-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>126838049</v>
       </c>
       <c r="B4" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
